--- a/data/data_raw/eurostat/AT_milk_apro_mk_colm.xlsx
+++ b/data/data_raw/eurostat/AT_milk_apro_mk_colm.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:PO15"/>
+  <dimension ref="A1:PU15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2577,6 +2577,36 @@
       <c r="PO1" s="1" t="inlineStr">
         <is>
           <t>2025-05</t>
+        </is>
+      </c>
+      <c r="PP1" s="1" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="PQ1" s="1" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="PR1" s="1" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="PS1" s="1" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="PT1" s="1" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="PU1" s="1" t="inlineStr">
+        <is>
+          <t>2025-11</t>
         </is>
       </c>
     </row>
@@ -3749,11 +3779,39 @@
       <c r="PJ2" t="n">
         <v>4.38</v>
       </c>
-      <c r="PK2" t="inlineStr"/>
-      <c r="PL2" t="inlineStr"/>
-      <c r="PM2" t="inlineStr"/>
-      <c r="PN2" t="inlineStr"/>
-      <c r="PO2" t="inlineStr"/>
+      <c r="PK2" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="PL2" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="PM2" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="PN2" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="PO2" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="PP2" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="PQ2" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="PR2" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="PS2" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="PT2" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="PU2" t="n">
+        <v>4.34</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -4939,6 +4997,24 @@
       <c r="PO3" t="n">
         <v>316.75</v>
       </c>
+      <c r="PP3" t="n">
+        <v>286.91</v>
+      </c>
+      <c r="PQ3" t="n">
+        <v>290.18</v>
+      </c>
+      <c r="PR3" t="n">
+        <v>282.83</v>
+      </c>
+      <c r="PS3" t="n">
+        <v>274.52</v>
+      </c>
+      <c r="PT3" t="n">
+        <v>287.58</v>
+      </c>
+      <c r="PU3" t="n">
+        <v>279.71</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -6109,11 +6185,39 @@
       <c r="PJ4" t="n">
         <v>3.56</v>
       </c>
-      <c r="PK4" t="inlineStr"/>
-      <c r="PL4" t="inlineStr"/>
-      <c r="PM4" t="inlineStr"/>
-      <c r="PN4" t="inlineStr"/>
-      <c r="PO4" t="inlineStr"/>
+      <c r="PK4" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="PL4" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="PM4" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="PN4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="PO4" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="PP4" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="PQ4" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="PR4" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="PS4" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="PT4" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="PU4" t="n">
+        <v>3.56</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -6855,6 +6959,12 @@
       <c r="PM5" t="inlineStr"/>
       <c r="PN5" t="inlineStr"/>
       <c r="PO5" t="inlineStr"/>
+      <c r="PP5" t="inlineStr"/>
+      <c r="PQ5" t="inlineStr"/>
+      <c r="PR5" t="inlineStr"/>
+      <c r="PS5" t="inlineStr"/>
+      <c r="PT5" t="inlineStr"/>
+      <c r="PU5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -7596,6 +7706,12 @@
       <c r="PM6" t="inlineStr"/>
       <c r="PN6" t="inlineStr"/>
       <c r="PO6" t="inlineStr"/>
+      <c r="PP6" t="inlineStr"/>
+      <c r="PQ6" t="inlineStr"/>
+      <c r="PR6" t="inlineStr"/>
+      <c r="PS6" t="inlineStr"/>
+      <c r="PT6" t="inlineStr"/>
+      <c r="PU6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -8337,6 +8453,12 @@
       <c r="PM7" t="inlineStr"/>
       <c r="PN7" t="inlineStr"/>
       <c r="PO7" t="inlineStr"/>
+      <c r="PP7" t="inlineStr"/>
+      <c r="PQ7" t="inlineStr"/>
+      <c r="PR7" t="inlineStr"/>
+      <c r="PS7" t="inlineStr"/>
+      <c r="PT7" t="inlineStr"/>
+      <c r="PU7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -9517,9 +9639,27 @@
         <v>61.61</v>
       </c>
       <c r="PN8" t="n">
-        <v>58.57</v>
-      </c>
-      <c r="PO8" t="inlineStr"/>
+        <v>60.92</v>
+      </c>
+      <c r="PO8" t="n">
+        <v>62.38</v>
+      </c>
+      <c r="PP8" t="n">
+        <v>53.76</v>
+      </c>
+      <c r="PQ8" t="n">
+        <v>54.01</v>
+      </c>
+      <c r="PR8" t="n">
+        <v>54.12</v>
+      </c>
+      <c r="PS8" t="n">
+        <v>57.21</v>
+      </c>
+      <c r="PT8" t="n">
+        <v>56.24</v>
+      </c>
+      <c r="PU8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -10700,9 +10840,27 @@
         <v>6.13</v>
       </c>
       <c r="PN9" t="n">
-        <v>5.98</v>
-      </c>
-      <c r="PO9" t="inlineStr"/>
+        <v>6.2</v>
+      </c>
+      <c r="PO9" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="PP9" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="PQ9" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="PR9" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="PS9" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="PT9" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="PU9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -11874,18 +12032,36 @@
         <v>0.32</v>
       </c>
       <c r="PK10" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="PL10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="PM10" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="PN10" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="PO10" t="n">
         <v>0.15</v>
       </c>
-      <c r="PL10" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="PM10" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="PN10" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="PO10" t="inlineStr"/>
+      <c r="PP10" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="PQ10" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="PR10" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="PS10" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="PT10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="PU10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -13057,18 +13233,36 @@
         <v>0.54</v>
       </c>
       <c r="PK11" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="PL11" t="n">
         <v>0.38</v>
       </c>
       <c r="PM11" t="n">
-        <v>0.43</v>
+        <v>0.37</v>
       </c>
       <c r="PN11" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="PO11" t="inlineStr"/>
+        <v>0.31</v>
+      </c>
+      <c r="PO11" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="PP11" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="PQ11" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="PR11" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="PS11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="PT11" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="PU11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -13644,6 +13838,12 @@
       <c r="PM12" t="inlineStr"/>
       <c r="PN12" t="inlineStr"/>
       <c r="PO12" t="inlineStr"/>
+      <c r="PP12" t="inlineStr"/>
+      <c r="PQ12" t="inlineStr"/>
+      <c r="PR12" t="inlineStr"/>
+      <c r="PS12" t="inlineStr"/>
+      <c r="PT12" t="inlineStr"/>
+      <c r="PU12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -14776,9 +14976,27 @@
         <v>27.83</v>
       </c>
       <c r="PN13" t="n">
-        <v>25.21</v>
-      </c>
-      <c r="PO13" t="inlineStr"/>
+        <v>26.28</v>
+      </c>
+      <c r="PO13" t="n">
+        <v>27.13</v>
+      </c>
+      <c r="PP13" t="n">
+        <v>27.75</v>
+      </c>
+      <c r="PQ13" t="n">
+        <v>30.28</v>
+      </c>
+      <c r="PR13" t="n">
+        <v>26.03</v>
+      </c>
+      <c r="PS13" t="n">
+        <v>28.29</v>
+      </c>
+      <c r="PT13" t="n">
+        <v>27.72</v>
+      </c>
+      <c r="PU13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -15959,9 +16177,27 @@
         <v>3.31</v>
       </c>
       <c r="PN14" t="n">
-        <v>3</v>
-      </c>
-      <c r="PO14" t="inlineStr"/>
+        <v>3.33</v>
+      </c>
+      <c r="PO14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="PP14" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="PQ14" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="PR14" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="PS14" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="PT14" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="PU14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -17142,9 +17378,27 @@
         <v>20.59</v>
       </c>
       <c r="PN15" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="PO15" t="inlineStr"/>
+        <v>22.34</v>
+      </c>
+      <c r="PO15" t="n">
+        <v>22.41</v>
+      </c>
+      <c r="PP15" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="PQ15" t="n">
+        <v>20.68</v>
+      </c>
+      <c r="PR15" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="PS15" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="PT15" t="n">
+        <v>21.17</v>
+      </c>
+      <c r="PU15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
